--- a/templates/2027/mock/03_攤位資料.xlsx
+++ b/templates/2027/mock/03_攤位資料.xlsx
@@ -23,7 +23,10 @@
           <t xml:space="preserve">必須 — 冇就唔成立
 型別：text
 例：A01
-唯一鍵。場地圖同遊戲卡認呢個</t>
+唯一鍵。場地圖同遊戲卡認呢個
+只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。
+✓ 可以：A01、B07、E12
+✗ 唔好：A1（唔夠兩位）、A1 Core（夾埋名）、A-01（有符號）</t>
         </r>
       </text>
     </comment>
@@ -88,7 +91,10 @@
         <r>
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：number
-例：7</t>
+例：7
+只准填整數。唔好填「7.0」「約7」「7人」。
+✓ 可以：7、0
+✗ 唔好：7.0、約7、7人、七</t>
         </r>
       </text>
     </comment>
@@ -98,7 +104,10 @@
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：number
 例：7
-影響代訂餐盒</t>
+影響代訂餐盒
+只准填整數。唔好填「7.0」「約7」「7人」。
+✓ 可以：7、0
+✗ 唔好：7.0、約7、7人、七</t>
         </r>
       </text>
     </comment>
@@ -107,7 +116,10 @@
         <r>
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：bool
-例：Y</t>
+例：Y
+只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。
+✓ 可以：Y、（留空）
+✗ 唔好：是、有、✓、1、TRUE</t>
         </r>
       </text>
     </comment>
@@ -721,7 +733,7 @@
     <t>級別</t>
   </si>
   <si>
-    <t>型別</t>
+    <t>格式</t>
   </si>
   <si>
     <t>例子</t>
@@ -730,12 +742,12 @@
     <t>說明</t>
   </si>
   <si>
+    <t>只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。　✓A01／B07／E12　✗A1（唔夠兩位）／A1 Core（夾埋名）／A-01（有符號）　唯一鍵。場地圖同遊戲卡認呢個</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
-    <t>唯一鍵。場地圖同遊戲卡認呢個</t>
-  </si>
-  <si>
     <t>由攤位編號第一個字自動取</t>
   </si>
   <si>
@@ -754,19 +766,19 @@
     <t>H</t>
   </si>
   <si>
-    <t>number</t>
+    <t>只准填整數。唔好填「7.0」「約7」「7人」。　✓7／0　✗7.0／約7／7人／七</t>
   </si>
   <si>
     <t>I</t>
   </si>
   <si>
-    <t>影響代訂餐盒</t>
+    <t>只准填整數。唔好填「7.0」「約7」「7人」。　✓7／0　✗7.0／約7／7人／七　影響代訂餐盒</t>
   </si>
   <si>
     <t>J</t>
   </si>
   <si>
-    <t>bool</t>
+    <t>只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。　✓Y／（留空）　✗是／有／✓／1／TRUE</t>
   </si>
   <si>
     <t>三級意思</t>
@@ -1214,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J533"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15.6" customWidth="1"/>
@@ -1291,1064 +1303,1570 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B501" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C501" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D501" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E501" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F501" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G501" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H501" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I501" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="J501" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B502" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C502" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D502" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E502" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F502" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G502" t="s">
         <v>17</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H502" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I502" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="J502" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B503" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C503" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D503" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E503" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F503" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G503" t="s">
         <v>17</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H503" t="s">
         <v>32</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I503" t="s">
         <v>32</v>
       </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="J503" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B504" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C504" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D504" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E504" t="s">
         <v>25</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F504" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G504" t="s">
         <v>17</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H504" t="s">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I504" t="s">
         <v>38</v>
       </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="J504" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B505" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C505" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D505" t="s">
         <v>41</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E505" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F505" t="s">
         <v>42</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G505" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H505" t="s">
         <v>38</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I505" t="s">
         <v>38</v>
       </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="J505" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
         <v>43</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B506" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C506" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D506" t="s">
         <v>45</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E506" t="s">
         <v>25</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F506" t="s">
         <v>46</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G506" t="s">
         <v>47</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H506" t="s">
         <v>48</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I506" t="s">
         <v>49</v>
       </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="J506" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B507" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C507" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D507" t="s">
         <v>52</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E507" t="s">
         <v>25</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F507" t="s">
         <v>53</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G507" t="s">
         <v>17</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H507" t="s">
         <v>48</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I507" t="s">
         <v>49</v>
       </c>
-      <c r="J9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="J507" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B508" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C508" t="s">
         <v>55</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D508" t="s">
         <v>56</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E508" t="s">
         <v>25</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F508" t="s">
         <v>57</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G508" t="s">
         <v>17</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H508" t="s">
         <v>27</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I508" t="s">
         <v>27</v>
       </c>
-      <c r="J10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="J508" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
         <v>58</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B509" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C509" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D509" t="s">
         <v>56</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E509" t="s">
         <v>25</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F509" t="s">
         <v>60</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G509" t="s">
         <v>17</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H509" t="s">
         <v>48</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I509" t="s">
         <v>48</v>
       </c>
-      <c r="J11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="J509" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B510" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C510" t="s">
         <v>62</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D510" t="s">
         <v>63</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E510" t="s">
         <v>25</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F510" t="s">
         <v>64</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G510" t="s">
         <v>17</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H510" t="s">
         <v>38</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I510" t="s">
         <v>65</v>
       </c>
-      <c r="J12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="J510" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
         <v>66</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B511" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C511" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D511" t="s">
         <v>68</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E511" t="s">
         <v>25</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F511" t="s">
         <v>69</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G511" t="s">
         <v>17</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H511" t="s">
         <v>32</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I511" t="s">
         <v>70</v>
       </c>
-      <c r="J13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="J511" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
         <v>71</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B512" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C512" t="s">
         <v>72</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D512" t="s">
         <v>73</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E512" t="s">
         <v>25</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F512" t="s">
         <v>74</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G512" t="s">
         <v>17</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H512" t="s">
         <v>38</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I512" t="s">
         <v>38</v>
       </c>
-      <c r="J14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="J512" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
         <v>75</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B513" t="s">
         <v>76</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C513" t="s">
         <v>77</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D513" t="s">
         <v>78</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E513" t="s">
         <v>79</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F513" t="s">
         <v>80</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G513" t="s">
         <v>81</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H513" t="s">
         <v>48</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I513" t="s">
         <v>70</v>
       </c>
-      <c r="J15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="J513" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
         <v>82</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B514" t="s">
         <v>76</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C514" t="s">
         <v>83</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D514" t="s">
         <v>83</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E514" t="s">
         <v>79</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F514" t="s">
         <v>84</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G514" t="s">
         <v>19</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H514" t="s">
         <v>38</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I514" t="s">
         <v>65</v>
       </c>
-      <c r="J16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="J514" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
         <v>85</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B515" t="s">
         <v>76</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C515" t="s">
         <v>86</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D515" t="s">
         <v>87</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E515" t="s">
         <v>79</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F515" t="s">
         <v>88</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G515" t="s">
         <v>89</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H515" t="s">
         <v>37</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I515" t="s">
         <v>90</v>
       </c>
-      <c r="J17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="J515" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
         <v>91</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B516" t="s">
         <v>92</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C516" t="s">
         <v>93</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D516" t="s">
         <v>94</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E516" t="s">
         <v>95</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F516" t="s">
         <v>96</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G516" t="s">
         <v>19</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H516" t="s">
         <v>48</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I516" t="s">
         <v>49</v>
       </c>
-      <c r="J18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="J516" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
         <v>97</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B517" t="s">
         <v>92</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C517" t="s">
         <v>98</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D517" t="s">
         <v>99</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E517" t="s">
         <v>95</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F517" t="s">
         <v>100</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G517" t="s">
         <v>101</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H517" t="s">
         <v>20</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I517" t="s">
         <v>102</v>
       </c>
-      <c r="J19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="J517" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
         <v>103</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B518" t="s">
         <v>92</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C518" t="s">
         <v>104</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D518" t="s">
         <v>105</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E518" t="s">
         <v>95</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F518" t="s">
         <v>106</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G518" t="s">
         <v>107</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H518" t="s">
         <v>108</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I518" t="s">
         <v>109</v>
       </c>
-      <c r="J20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="J518" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
         <v>110</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B519" t="s">
         <v>92</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C519" t="s">
         <v>111</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D519" t="s">
         <v>112</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E519" t="s">
         <v>95</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F519" t="s">
         <v>113</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G519" t="s">
         <v>114</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H519" t="s">
         <v>115</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I519" t="s">
         <v>116</v>
       </c>
-      <c r="J21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="J519" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
         <v>117</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B520" t="s">
         <v>118</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C520" t="s">
         <v>119</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D520" t="s">
         <v>120</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E520" t="s">
         <v>121</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F520" t="s">
         <v>119</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G520" t="s">
         <v>122</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H520" t="s">
         <v>17</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I520" t="s">
         <v>123</v>
       </c>
-      <c r="J22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="J520" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
         <v>124</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B521" t="s">
         <v>118</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C521" t="s">
         <v>125</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D521" t="s">
         <v>126</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E521" t="s">
         <v>121</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F521" t="s">
         <v>125</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G521" t="s">
         <v>127</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H521" t="s">
         <v>17</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I521" t="s">
         <v>123</v>
       </c>
-      <c r="J23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="J521" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
         <v>128</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B522" t="s">
         <v>118</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C522" t="s">
         <v>129</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D522" t="s">
         <v>130</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E522" t="s">
         <v>121</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F522" t="s">
         <v>129</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G522" t="s">
         <v>17</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H522" t="s">
         <v>17</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I522" t="s">
         <v>123</v>
       </c>
-      <c r="J24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="J522" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
         <v>131</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B523" t="s">
         <v>118</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C523" t="s">
         <v>132</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D523" t="s">
         <v>133</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E523" t="s">
         <v>121</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F523" t="s">
         <v>134</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G523" t="s">
         <v>135</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H523" t="s">
         <v>136</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I523" t="s">
         <v>37</v>
       </c>
-      <c r="J25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="J523" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
         <v>137</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B524" t="s">
         <v>118</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C524" t="s">
         <v>138</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D524" t="s">
         <v>139</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E524" t="s">
         <v>121</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F524" t="s">
         <v>140</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G524" t="s">
         <v>17</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H524" t="s">
         <v>136</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I524" t="s">
         <v>37</v>
       </c>
-      <c r="J26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="J524" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
         <v>141</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B525" t="s">
         <v>142</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C525" t="s">
         <v>143</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D525" t="s">
         <v>144</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E525" t="s">
         <v>145</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F525" t="s">
         <v>146</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G525" t="s">
         <v>147</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H525" t="s">
         <v>108</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I525" t="s">
         <v>38</v>
       </c>
-      <c r="J27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="J525" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
         <v>148</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B526" t="s">
         <v>142</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C526" t="s">
         <v>149</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D526" t="s">
         <v>150</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E526" t="s">
         <v>145</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F526" t="s">
         <v>146</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G526" t="s">
         <v>17</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H526" t="s">
         <v>108</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I526" t="s">
         <v>38</v>
       </c>
-      <c r="J28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="J526" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
         <v>151</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B527" t="s">
         <v>142</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C527" t="s">
         <v>152</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D527" t="s">
         <v>153</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E527" t="s">
         <v>145</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F527" t="s">
         <v>154</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G527" t="s">
         <v>17</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H527" t="s">
         <v>27</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I527" t="s">
         <v>27</v>
       </c>
-      <c r="J29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="J527" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
         <v>155</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B528" t="s">
         <v>156</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C528" t="s">
         <v>157</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D528" t="s">
         <v>158</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E528" t="s">
         <v>159</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F528" t="s">
         <v>160</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G528" t="s">
         <v>17</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H528" t="s">
         <v>37</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I528" t="s">
         <v>90</v>
       </c>
-      <c r="J30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="J528" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
         <v>161</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B529" t="s">
         <v>156</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C529" t="s">
         <v>162</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D529" t="s">
         <v>163</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E529" t="s">
         <v>159</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F529" t="s">
         <v>164</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G529" t="s">
         <v>165</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H529" t="s">
         <v>37</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I529" t="s">
         <v>90</v>
       </c>
-      <c r="J31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="J529" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
         <v>166</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B530" t="s">
         <v>156</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C530" t="s">
         <v>167</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D530" t="s">
         <v>168</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E530" t="s">
         <v>159</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F530" t="s">
         <v>169</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G530" t="s">
         <v>17</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H530" t="s">
         <v>136</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I530" t="s">
         <v>136</v>
       </c>
-      <c r="J32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="J530" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
         <v>170</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B531" t="s">
         <v>156</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C531" t="s">
         <v>171</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D531" t="s">
         <v>172</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E531" t="s">
         <v>159</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F531" t="s">
         <v>173</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G531" t="s">
         <v>174</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H531" t="s">
         <v>37</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I531" t="s">
         <v>90</v>
       </c>
-      <c r="J33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="J531" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
         <v>175</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B532" t="s">
         <v>156</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C532" t="s">
         <v>176</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D532" t="s">
         <v>176</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E532" t="s">
         <v>159</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F532" t="s">
         <v>177</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G532" t="s">
         <v>17</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H532" t="s">
         <v>178</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I532" t="s">
         <v>178</v>
       </c>
-      <c r="J34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="J532" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
         <v>179</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B533" t="s">
         <v>156</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C533" t="s">
         <v>180</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D533" t="s">
         <v>181</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E533" t="s">
         <v>159</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F533" t="s">
         <v>182</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G533" t="s">
         <v>19</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H533" t="s">
         <v>37</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I533" t="s">
         <v>90</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J533" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="6">
+    <dataValidation showInputMessage="1" promptTitle="攤位編號　格式" prompt="只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。  ✓ 可以：A01、B07、E12 ✗ 唔好：A1（唔夠兩位）、A1 Core（夾埋名）、A-01（有符號）" sqref="A10:A500"/>
+    <dataValidation showInputMessage="1" promptTitle="攤位編號　格式" prompt="只准填編號本身：一個英文區碼 ＋ 兩位數字。攤位名稱填落「攤位名稱」嗰欄。  ✓ 可以：A01、B07、E12 ✗ 唔好：A1（唔夠兩位）、A1 Core（夾埋名）、A-01（有符號）" sqref="A3:A500"/>
+    <dataValidation showInputMessage="1" promptTitle="數目　格式" prompt="只准填整數。唔好填「7.0」「約7」「7人」。  ✓ 可以：7、0 ✗ 唔好：7.0、約7、7人、七" sqref="H10:I500"/>
+    <dataValidation showInputMessage="1" promptTitle="數目　格式" prompt="只准填整數。唔好填「7.0」「約7」「7人」。  ✓ 可以：7、0 ✗ 唔好：7.0、約7、7人、七" sqref="H3:I500"/>
+    <dataValidation showInputMessage="1" promptTitle="是／否　格式" prompt="只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。  ✓ 可以：Y、（留空） ✗ 唔好：是、有、✓、1、TRUE" sqref="J10:J500"/>
+    <dataValidation showInputMessage="1" promptTitle="是／否　格式" prompt="只准填 Y 或者留空。唔好填「是」「有」「✓」「1」。  ✓ 可以：Y、（留空） ✗ 唔好：是、有、✓、1、TRUE" sqref="J3:J500"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -2462,13 +2980,13 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>204</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,7 +3000,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -2502,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2522,7 +3040,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
@@ -2542,7 +3060,7 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
@@ -2562,7 +3080,7 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E17" t="s">
         <v>207</v>
@@ -2582,7 +3100,7 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E18" t="s">
         <v>209</v>
@@ -2602,13 +3120,13 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>212</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
         <v>102</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2622,7 +3140,7 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>212</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>102</v>
@@ -2642,13 +3160,13 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>216</v>
-      </c>
-      <c r="E21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
